--- a/Portafolio.xlsx
+++ b/Portafolio.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jugonz\Downloads\TradingInvest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B26D081-E7F1-4C7D-B759-2CCB69713A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026D08D4-CE27-4F58-93C0-71D563CF73C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transacciones" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Transacciones!$A$1:$H$40</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="42">
   <si>
     <t>Ticker</t>
   </si>
@@ -99,6 +102,69 @@
   </si>
   <si>
     <t>HALO</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Large Value</t>
+  </si>
+  <si>
+    <t>Large Blend</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Empresa / Fondo</t>
+  </si>
+  <si>
+    <t>NVIDIA Corp.</t>
+  </si>
+  <si>
+    <t>Broadcom Inc.</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Google)</t>
+  </si>
+  <si>
+    <t>Amazon.com Inc.</t>
+  </si>
+  <si>
+    <t>MercadoLibre Inc.</t>
+  </si>
+  <si>
+    <t>Nubank (Nu Holdings)</t>
+  </si>
+  <si>
+    <t>Vanguard S&amp;P 500 ETF</t>
+  </si>
+  <si>
+    <t>Schwab US Dividend Equity</t>
+  </si>
+  <si>
+    <t>Microsoft Corporation</t>
+  </si>
+  <si>
+    <t>Meta Platforms, Inc.</t>
+  </si>
+  <si>
+    <t>Veeva Systems Inc.</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
+    <t>Halozyme Therapeutics</t>
+  </si>
+  <si>
+    <t>Vanguard Dividend Appreciation ETF</t>
   </si>
 </sst>
 </file>
@@ -110,7 +176,7 @@
     <numFmt numFmtId="165" formatCode="0.000000000"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +195,18 @@
       <sz val="11"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -178,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -206,6 +284,15 @@
     </xf>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -471,817 +558,1060 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="2" max="2" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="3">
         <v>46098</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="4">
         <v>5.4791517999999997E-2</v>
       </c>
-      <c r="E2" s="5">
+      <c r="G2" s="5">
         <v>10</v>
       </c>
-      <c r="F2" s="5">
+      <c r="H2" s="5">
         <v>182.51</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="3">
         <v>46098</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="4">
         <v>0.32372936200000002</v>
       </c>
-      <c r="E3" s="5">
+      <c r="G3" s="5">
         <v>10</v>
       </c>
-      <c r="F3" s="5">
+      <c r="H3" s="5">
         <v>30.89</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3">
         <v>46098</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4">
         <v>8.1333875E-2</v>
       </c>
-      <c r="E4" s="5">
+      <c r="G4" s="5">
         <v>50</v>
       </c>
-      <c r="F4" s="5">
+      <c r="H4" s="5">
         <v>614.74</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3">
         <v>46100</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="E5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="4">
         <v>1.014796386</v>
       </c>
-      <c r="E5" s="5">
+      <c r="G5" s="5">
         <v>31</v>
       </c>
-      <c r="F5" s="5">
+      <c r="H5" s="5">
         <v>30.55</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3">
         <v>46100</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4">
         <v>5.6305933000000002E-2</v>
       </c>
-      <c r="E6" s="5">
+      <c r="G6" s="5">
         <v>34</v>
       </c>
-      <c r="F6" s="5">
+      <c r="H6" s="5">
         <v>603.86</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
         <v>46101</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="E7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4">
         <v>9.6860742999999999E-2</v>
       </c>
-      <c r="E7" s="5">
+      <c r="G7" s="5">
         <v>20</v>
       </c>
-      <c r="F7" s="5">
+      <c r="H7" s="5">
         <v>206.48</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3">
         <v>46101</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="E8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="4">
         <v>9.8165225999999994E-2</v>
       </c>
-      <c r="E8" s="5">
+      <c r="G8" s="5">
         <v>30.55</v>
       </c>
-      <c r="F8" s="5">
+      <c r="H8" s="5">
         <v>311.22000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="3">
         <v>46101</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4">
         <v>0.13437970299999999</v>
       </c>
-      <c r="E9" s="5">
+      <c r="G9" s="5">
         <v>40</v>
       </c>
-      <c r="F9" s="5">
+      <c r="H9" s="5">
         <v>297.68</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="3">
         <v>46101</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="E10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="4">
         <v>1.4411298450000001</v>
       </c>
-      <c r="E10" s="5">
+      <c r="G10" s="5">
         <v>20</v>
       </c>
-      <c r="F10" s="5">
+      <c r="H10" s="5">
         <v>13.88</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="3">
         <v>46101</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="E11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="4">
         <v>0.493129068</v>
       </c>
-      <c r="E11" s="5">
+      <c r="G11" s="5">
         <v>15</v>
       </c>
-      <c r="F11" s="5">
+      <c r="H11" s="5">
         <v>30.42</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="3">
         <v>46101</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="E12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="4">
         <v>0.116320806</v>
       </c>
-      <c r="E12" s="5">
+      <c r="G12" s="5">
         <v>70</v>
       </c>
-      <c r="F12" s="5">
+      <c r="H12" s="5">
         <v>601.80999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="3">
         <v>46107</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="E13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="4">
         <v>7.0015753E-2</v>
       </c>
-      <c r="E13" s="5">
+      <c r="G13" s="5">
         <v>20</v>
       </c>
-      <c r="F13" s="5">
+      <c r="H13" s="5">
         <v>285.64999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="3">
         <v>46107</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="E14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="4">
         <v>2.0099586999999999E-2</v>
       </c>
-      <c r="E14" s="5">
+      <c r="G14" s="5">
         <v>33.35</v>
       </c>
-      <c r="F14" s="5">
+      <c r="H14" s="5">
         <v>1659.24</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="3">
         <v>46107</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="E15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="4">
         <v>7.4759275E-2</v>
       </c>
-      <c r="E15" s="5">
+      <c r="G15" s="5">
         <v>45</v>
       </c>
-      <c r="F15" s="5">
+      <c r="H15" s="5">
         <v>601.88</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="3">
         <v>46107</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="4">
+      <c r="E16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="4">
         <v>7.4621172999999999E-2</v>
       </c>
-      <c r="E16" s="5">
+      <c r="G16" s="5">
         <v>45</v>
       </c>
-      <c r="F16" s="5">
+      <c r="H16" s="5">
         <v>602.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="7">
         <v>46107</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="E17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="8">
+      <c r="F17" s="8">
         <v>-4.9735408000000002E-2</v>
       </c>
-      <c r="E17" s="9">
+      <c r="G17" s="9">
         <v>30</v>
       </c>
-      <c r="F17" s="9">
+      <c r="H17" s="9">
         <v>603.14</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="3">
         <v>46108</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="E18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="4">
         <v>3.842661E-2</v>
       </c>
-      <c r="E18" s="5">
+      <c r="G18" s="5">
         <v>61.61</v>
       </c>
-      <c r="F18" s="5">
+      <c r="H18" s="5">
         <v>1603.87</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="3">
         <v>46111</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="4">
+      <c r="E19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="4">
         <v>0.13236134999999999</v>
       </c>
-      <c r="E19" s="5">
+      <c r="G19" s="5">
         <v>47.68</v>
       </c>
-      <c r="F19" s="5">
+      <c r="H19" s="5">
         <v>360.21</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="3">
         <v>46113</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="4">
+      <c r="E20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="4">
         <v>0.40260699799999999</v>
       </c>
-      <c r="E20" s="5">
+      <c r="G20" s="5">
         <v>85</v>
       </c>
-      <c r="F20" s="5">
+      <c r="H20" s="5">
         <v>211.12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="3">
         <v>46113</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="4">
+      <c r="E21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="4">
         <v>0.27243873499999999</v>
       </c>
-      <c r="E21" s="5">
+      <c r="G21" s="5">
         <v>80</v>
       </c>
-      <c r="F21" s="5">
+      <c r="H21" s="5">
         <v>293.68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="3">
         <v>46113</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="4">
+      <c r="E22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="4">
         <v>3.7768475000000003E-2</v>
       </c>
-      <c r="E22" s="5">
+      <c r="G22" s="5">
         <v>65</v>
       </c>
-      <c r="F22" s="5">
+      <c r="H22" s="5">
         <v>1720.6</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="3">
         <v>46113</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="4">
+      <c r="E23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="4">
         <v>0.25582059099999999</v>
       </c>
-      <c r="E23" s="5">
+      <c r="G23" s="5">
         <v>95</v>
       </c>
-      <c r="F23" s="5">
+      <c r="H23" s="5">
         <v>371.35</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="3">
         <v>46113</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="4">
+      <c r="E24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="4">
         <v>0.62468765599999998</v>
       </c>
-      <c r="E24" s="5">
+      <c r="G24" s="5">
         <v>110</v>
       </c>
-      <c r="F24" s="5">
+      <c r="H24" s="5">
         <v>176.09</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="3">
         <v>46113</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="4">
+      <c r="E25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="4">
         <v>4.0238156999999997E-2</v>
       </c>
-      <c r="E25" s="5">
+      <c r="G25" s="5">
         <v>1.23</v>
       </c>
-      <c r="F25" s="5">
+      <c r="H25" s="5">
         <v>30.57</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="3">
         <v>46113</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="4">
+      <c r="E26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="4">
         <v>0.30101232700000002</v>
       </c>
-      <c r="E26" s="5">
+      <c r="G26" s="5">
         <v>65</v>
       </c>
-      <c r="F26" s="5">
+      <c r="H26" s="5">
         <v>215.94</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="3">
         <v>46120</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="4">
+      <c r="E27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="4">
         <v>0.158218835</v>
       </c>
-      <c r="E27" s="5">
+      <c r="G27" s="5">
         <v>50</v>
       </c>
-      <c r="F27" s="5">
+      <c r="H27" s="5">
         <v>316.02</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="3">
         <v>46120</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="4">
+      <c r="E28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="4">
         <v>0.129870129</v>
       </c>
-      <c r="E28" s="5">
+      <c r="G28" s="5">
         <v>50</v>
       </c>
-      <c r="F28" s="5">
+      <c r="H28" s="5">
         <v>385.01</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="3">
         <v>46122</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="4">
+      <c r="E29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="4">
         <v>9.9431818000000005E-2</v>
       </c>
-      <c r="E29" s="5">
+      <c r="G29" s="5">
         <v>37.17</v>
       </c>
-      <c r="F29" s="5">
+      <c r="H29" s="5">
         <v>373.83</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="3">
         <v>46122</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="4">
+      <c r="E30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="4">
         <v>0.15856706100000001</v>
       </c>
-      <c r="E30" s="5">
+      <c r="G30" s="5">
         <v>50</v>
       </c>
-      <c r="F30" s="5">
+      <c r="H30" s="5">
         <v>315.33</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="3">
         <v>46122</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="4">
+      <c r="E31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="4">
         <v>0.13501909100000001</v>
       </c>
-      <c r="E31" s="5">
+      <c r="G31" s="5">
         <v>50</v>
       </c>
-      <c r="F31" s="5">
+      <c r="H31" s="5">
         <v>370.32</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="3">
         <v>46148</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="4">
+      <c r="E32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="4">
         <v>3.7920067000000002E-2</v>
       </c>
-      <c r="E32" s="5">
+      <c r="G32" s="5">
         <v>70.010000000000005</v>
       </c>
-      <c r="F32" s="5">
+      <c r="H32" s="5">
         <v>1846.17</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="3">
         <v>46148</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="4">
+      <c r="E33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="4">
         <v>2.083619288</v>
       </c>
-      <c r="E33" s="5">
+      <c r="G33" s="5">
         <v>30</v>
       </c>
-      <c r="F33" s="5">
+      <c r="H33" s="5">
         <v>14.4</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="3">
         <v>46149</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="4">
+      <c r="E34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="4">
         <v>6.305181535</v>
       </c>
-      <c r="E34" s="5">
+      <c r="G34" s="5">
         <v>90.1</v>
       </c>
-      <c r="F34" s="5">
+      <c r="H34" s="5">
         <v>14.29</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="3">
         <v>46149</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="4">
+      <c r="E35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="4">
         <v>0.63395460800000003</v>
       </c>
-      <c r="E35" s="5">
+      <c r="G35" s="5">
         <v>20</v>
       </c>
-      <c r="F35" s="5">
+      <c r="H35" s="5">
         <v>31.55</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" s="3">
         <v>46168</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="4">
+      <c r="E36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="4">
         <v>0.16452455599999999</v>
       </c>
-      <c r="E36" s="5">
+      <c r="G36" s="5">
         <v>100</v>
       </c>
-      <c r="F36" s="5">
+      <c r="H36" s="5">
         <v>607.78</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="3">
         <v>46185</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="4">
+      <c r="E37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="4">
         <v>0.14874000100000001</v>
       </c>
-      <c r="E37" s="5">
+      <c r="G37" s="5">
         <v>84.05</v>
       </c>
-      <c r="F37" s="5">
+      <c r="H37" s="5">
         <v>565.04999999999995</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="3">
         <v>46202</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="4">
+      <c r="E38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="4">
         <v>0.56388221599999999</v>
       </c>
-      <c r="E38" s="5">
+      <c r="G38" s="5">
         <v>100</v>
       </c>
-      <c r="F38" s="5">
+      <c r="H38" s="5">
         <v>177.34</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="3">
         <v>46195</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="4">
+      <c r="E39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="4">
         <v>1.0148342050000001</v>
       </c>
-      <c r="E39" s="5">
+      <c r="G39" s="5">
         <v>69.78</v>
       </c>
-      <c r="F39" s="5">
+      <c r="H39" s="5">
         <v>68.760000000000005</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="3">
         <v>46196</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="4">
+      <c r="E40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" s="4">
         <v>1.419199492</v>
       </c>
-      <c r="E40" s="5">
+      <c r="G40" s="5">
         <v>98.43</v>
       </c>
-      <c r="F40" s="5">
+      <c r="H40" s="5">
         <v>69.349999999999994</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H40" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
